--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>59.93382573127747</v>
+        <v>63.21707963943481</v>
       </c>
       <c r="E2" t="n">
         <v>0.9895301128904705</v>
@@ -503,7 +503,7 @@
         <v>0.9917649260714955</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9997048406139315</v>
+        <v>0.9997048406139316</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>101.0880675315857</v>
+        <v>101.4442019462585</v>
       </c>
       <c r="E3" t="n">
         <v>0.9934103815702056</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>59.93382573127747</v>
+        <v>63.21707963943481</v>
       </c>
       <c r="E2" t="n">
         <v>0.9895301128904705</v>
@@ -634,7 +634,7 @@
         <v>0.9917649260714955</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9997048406139315</v>
+        <v>0.9997048406139316</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>101.0880675315857</v>
+        <v>101.4442019462585</v>
       </c>
       <c r="E3" t="n">
         <v>0.9934103815702056</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>63.21707963943481</v>
+        <v>39.05030608177185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9895301128904705</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9997048406139316</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>101.4442019462585</v>
+        <v>61.92200469970703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9934103815702056</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9997048406139315</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>63.21707963943481</v>
+        <v>39.05030608177185</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9895301128904705</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9997048406139316</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>101.4442019462585</v>
+        <v>61.92200469970703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9934103815702056</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
         <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9917649260714955</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9997048406139315</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 5, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>39.05030608177185</v>
+        <v>63.98757123947144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8301299430800388</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8299319727891157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7727737585312433</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9688324309315561</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
+          <t>{'max_depth': 7, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>61.92200469970703</v>
+        <v>107.2460434436798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8401228194315976</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8043311830213942</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9671548891665509</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
+          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>198.3473773002625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8420706725609115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8707482993197279</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7989511082401389</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.96836387616271</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 150}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>39.05030608177185</v>
+        <v>63.98757123947144</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.8301299430800388</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8299319727891157</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.7727737585312433</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9688324309315561</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
+          <t>{'max_depth': 7, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>61.92200469970703</v>
+        <v>107.2460434436798</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.8401228194315976</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.8775510204081632</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.8043311830213942</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9671548891665509</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 49}</t>
+          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>198.3473773002625</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8420706725609115</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8707482993197279</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7989511082401389</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.96836387616271</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 150}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>63.98757123947144</v>
+        <v>238.5478436946869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8301299430800388</v>
+        <v>0.9284964745698829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8299319727891157</v>
+        <v>0.9487917146144994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7727737585312433</v>
+        <v>0.9299714828079678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9688324309315561</v>
+        <v>0.9855738312016764</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>107.2460434436798</v>
+        <v>542.2999491691589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8401228194315976</v>
+        <v>0.9297969871967362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8043311830213942</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9671548891665509</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>198.3473773002625</v>
+        <v>1223.890587806702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8420706725609115</v>
+        <v>0.9320954548153093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7989511082401389</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96836387616271</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 150}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>63.98757123947144</v>
+        <v>238.5478436946869</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8301299430800388</v>
+        <v>0.9284964745698829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8299319727891157</v>
+        <v>0.9487917146144994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7727737585312433</v>
+        <v>0.9299714828079678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9688324309315561</v>
+        <v>0.9855738312016764</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': 7, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 5, 'n_estimators': 49}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>107.2460434436798</v>
+        <v>542.2999491691589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8401228194315976</v>
+        <v>0.9297969871967362</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8043311830213942</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9671548891665509</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>198.3473773002625</v>
+        <v>1223.890587806702</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8420706725609115</v>
+        <v>0.9320954548153093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8707482993197279</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7989511082401389</v>
+        <v>0.9307583200797884</v>
       </c>
       <c r="H4" t="n">
-        <v>0.96836387616271</v>
+        <v>0.9854701839005708</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 150}</t>
+          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>238.5478436946869</v>
+        <v>26.29688501358032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284964745698829</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9487917146144994</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9299714828079678</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9855738312016764</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>542.2999491691589</v>
+        <v>44.4428026676178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9297969871967362</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9307583200797884</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854701839005708</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1223.890587806702</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9320954548153093</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9307583200797884</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9854701839005708</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>238.5478436946869</v>
+        <v>26.29688501358032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9284964745698829</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9487917146144994</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9299714828079678</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9855738312016764</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>542.2999491691589</v>
+        <v>44.4428026676178</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9297969871967362</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9307583200797884</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854701839005708</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1223.890587806702</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9320954548153093</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9493670886075949</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9307583200797884</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9854701839005708</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'max_depth': None, 'max_features': None, 'min_samples_leaf': 2, 'min_samples_split': 10, 'n_estimators': 200}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.29688501358032</v>
+        <v>36.34607529640198</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>44.4428026676178</v>
+        <v>57.35688400268555</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.29688501358032</v>
+        <v>36.34607529640198</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>44.4428026676178</v>
+        <v>57.35688400268555</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>36.34607529640198</v>
+        <v>38.76327848434448</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.35688400268555</v>
+        <v>59.45050168037415</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>36.34607529640198</v>
+        <v>38.76327848434448</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>57.35688400268555</v>
+        <v>59.45050168037415</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>38.76327848434448</v>
+        <v>2.305255174636841</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -507,7 +507,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>59.45050168037415</v>
+        <v>1.117658853530884</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -542,7 +542,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>38.76327848434448</v>
+        <v>2.305255174636841</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>59.45050168037415</v>
+        <v>1.117658853530884</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -673,7 +673,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.305255174636841</v>
+        <v>8.916476964950562</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117658853530884</v>
+        <v>17.79089164733887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.305255174636841</v>
+        <v>8.916476964950562</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.117658853530884</v>
+        <v>17.79089164733887</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.916476964950562</v>
+        <v>4.839031219482422</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>0.3627322096337217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.6887755102040817</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.5083156111307886</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.9442759961127307</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79089164733887</v>
+        <v>5.246864795684814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>0.3903824804094579</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.6887755102040817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.5083156111307886</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.9442759961127307</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>8.916476964950562</v>
+        <v>4.839031219482422</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>0.3627322096337217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.6887755102040817</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.5083156111307886</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.9442759961127307</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>17.79089164733887</v>
+        <v>5.246864795684814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>0.3903824804094579</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>0.6887755102040817</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>0.5083156111307886</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>0.9442759961127307</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.839031219482422</v>
+        <v>46.42610740661621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3627322096337217</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6887755102040817</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5083156111307886</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9442759961127307</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.246864795684814</v>
+        <v>67.93033361434937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3903824804094579</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6887755102040817</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5083156111307886</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9442759961127307</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.839031219482422</v>
+        <v>46.42610740661621</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3627322096337217</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6887755102040817</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5083156111307886</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9442759961127307</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.246864795684814</v>
+        <v>67.93033361434937</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3903824804094579</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6887755102040817</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5083156111307886</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9442759961127307</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>46.42610740661621</v>
+        <v>2.268043518066406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>67.93033361434937</v>
+        <v>1.16223406791687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>46.42610740661621</v>
+        <v>2.268043518066406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>67.93033361434937</v>
+        <v>1.16223406791687</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.268043518066406</v>
+        <v>2.095865249633789</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16223406791687</v>
+        <v>1.0072021484375</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.268043518066406</v>
+        <v>2.095865249633789</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.16223406791687</v>
+        <v>1.0072021484375</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095865249633789</v>
+        <v>2.101096153259277</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0072021484375</v>
+        <v>1.965266942977905</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -541,6 +541,41 @@
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.148327827453613</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.095865249633789</v>
+        <v>2.101096153259277</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -657,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0072021484375</v>
+        <v>1.965266942977905</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -672,6 +707,41 @@
         <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.148327827453613</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.101096153259277</v>
+        <v>2.696815729141235</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.965266942977905</v>
+        <v>1.548275232315063</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.148327827453613</v>
+        <v>2.652801275253296</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.101096153259277</v>
+        <v>2.696815729141235</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.965266942977905</v>
+        <v>1.548275232315063</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.148327827453613</v>
+        <v>2.652801275253296</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.696815729141235</v>
+        <v>2.815093755722046</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.548275232315063</v>
+        <v>1.426376581192017</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.652801275253296</v>
+        <v>2.55407977104187</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.696815729141235</v>
+        <v>2.815093755722046</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.548275232315063</v>
+        <v>1.426376581192017</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.652801275253296</v>
+        <v>2.55407977104187</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.815093755722046</v>
+        <v>10.47228741645813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426376581192017</v>
+        <v>12.85234880447388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.55407977104187</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.815093755722046</v>
+        <v>10.47228741645813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9259372549984396</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.426376581192017</v>
+        <v>12.85234880447388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.9296254451309558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9490794016110472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9303364774002756</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9854205054555963</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2.55407977104187</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47228741645813</v>
+        <v>15.33869910240173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12.85234880447388</v>
+        <v>22.75333476066589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>10.47228741645813</v>
+        <v>15.33869910240173</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9259372549984396</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>12.85234880447388</v>
+        <v>22.75333476066589</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9296254451309558</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9490794016110472</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9303364774002756</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9854205054555963</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15.33869910240173</v>
+        <v>20.4457700252533</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22.75333476066589</v>
+        <v>29.11326050758362</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>15.33869910240173</v>
+        <v>20.4457700252533</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22.75333476066589</v>
+        <v>29.11326050758362</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4457700252533</v>
+        <v>34.96213316917419</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.11326050758362</v>
+        <v>49.15799784660339</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>20.4457700252533</v>
+        <v>34.96213316917419</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.7424679277285154</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>29.11326050758362</v>
+        <v>49.15799784660339</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.7591605966879464</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.9409678236635419</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.7807709920516013</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.90826124945391</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>34.96213316917419</v>
+        <v>61.78164196014404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9427398491413124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9546202680460851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9468293212200711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9903869894713397</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>49.15799784660339</v>
+        <v>102.1410129070282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9447134275511153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9557959087702798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9481739773427895</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9901331238317979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>34.96213316917419</v>
+        <v>61.78164196014404</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7424679277285154</v>
+        <v>0.9427398491413124</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9546202680460851</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9468293212200711</v>
       </c>
       <c r="H2" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9903869894713397</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>49.15799784660339</v>
+        <v>102.1410129070282</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7591605966879464</v>
+        <v>0.9447134275511153</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9409678236635419</v>
+        <v>0.9557959087702798</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7807709920516013</v>
+        <v>0.9481739773427895</v>
       </c>
       <c r="H3" t="n">
-        <v>0.90826124945391</v>
+        <v>0.9901331238317979</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.78164196014404</v>
+        <v>61.46988463401794</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9427398491413124</v>
+        <v>0.5895628446209965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9546202680460851</v>
+        <v>0.8467190271091969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9468293212200711</v>
+        <v>0.6207954670261672</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9903869894713397</v>
+        <v>0.9675881513150331</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>102.1410129070282</v>
+        <v>89.66563558578491</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9447134275511153</v>
+        <v>0.6083215369454393</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9557959087702798</v>
+        <v>0.8467190271091969</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9481739773427895</v>
+        <v>0.6207954670261672</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9901331238317979</v>
+        <v>0.9675881513150331</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.78164196014404</v>
+        <v>61.46988463401794</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9427398491413124</v>
+        <v>0.5895628446209965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9546202680460851</v>
+        <v>0.8467190271091969</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9468293212200711</v>
+        <v>0.6207954670261672</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9903869894713397</v>
+        <v>0.9675881513150331</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>102.1410129070282</v>
+        <v>89.66563558578491</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9447134275511153</v>
+        <v>0.6083215369454393</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9557959087702798</v>
+        <v>0.8467190271091969</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9481739773427895</v>
+        <v>0.6207954670261672</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9901331238317979</v>
+        <v>0.9675881513150331</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.46988463401794</v>
+        <v>113.2630970478058</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5895628446209965</v>
+        <v>0.3720115955028341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8467190271091969</v>
+        <v>0.7020408163265306</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6207954670261672</v>
+        <v>0.5078676263535075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9675881513150331</v>
+        <v>0.9497494099680689</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>89.66563558578491</v>
+        <v>207.853880405426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6083215369454393</v>
+        <v>0.3973386578538888</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8467190271091969</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6207954670261672</v>
+        <v>0.4908803299777239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9675881513150331</v>
+        <v>0.9468468867138693</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>61.46988463401794</v>
+        <v>113.2630970478058</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5895628446209965</v>
+        <v>0.3720115955028341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8467190271091969</v>
+        <v>0.7020408163265306</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6207954670261672</v>
+        <v>0.5078676263535075</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9675881513150331</v>
+        <v>0.9497494099680689</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>89.66563558578491</v>
+        <v>207.853880405426</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6083215369454393</v>
+        <v>0.3973386578538888</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8467190271091969</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6207954670261672</v>
+        <v>0.4908803299777239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9675881513150331</v>
+        <v>0.9468468867138693</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>113.2630970478058</v>
+        <v>3.046119689941406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3720115955028341</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7020408163265306</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5078676263535075</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9497494099680689</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>207.853880405426</v>
+        <v>1.356411695480347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3973386578538888</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6836734693877551</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4908803299777239</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9468468867138693</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.451043128967285</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>113.2630970478058</v>
+        <v>3.046119689941406</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3720115955028341</v>
+        <v>0.9983593504958139</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7020408163265306</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5078676263535075</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9497494099680689</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 200}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>207.853880405426</v>
+        <v>1.356411695480347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3973386578538888</v>
+        <v>0.9983552409841592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6836734693877551</v>
+        <v>0.9935064935064936</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4908803299777239</v>
+        <v>0.9934996412139632</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9468468867138693</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'max_depth': None, 'max_features': 'sqrt', 'min_samples_leaf': 1, 'min_samples_split': 2, 'n_estimators': 50}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.451043128967285</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9983535762483131</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9935064935064936</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9934996412139632</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.046119689941406</v>
+        <v>4.011544466018677</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.356411695480347</v>
+        <v>2.477370738983154</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.451043128967285</v>
+        <v>4.23696756362915</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.046119689941406</v>
+        <v>4.011544466018677</v>
       </c>
       <c r="E2" t="n">
         <v>0.9983593504958139</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.356411695480347</v>
+        <v>2.477370738983154</v>
       </c>
       <c r="E3" t="n">
         <v>0.9983552409841592</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>2.451043128967285</v>
+        <v>4.23696756362915</v>
       </c>
       <c r="E4" t="n">
         <v>0.9983535762483131</v>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.011544466018677</v>
+        <v>18.47461676597595</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9130844517233803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9266891891891892</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9193123612301874</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9787282333085371</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2.477370738983154</v>
+        <v>34.06773924827576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.913262433288194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9263513513513514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9191034179457824</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9772424591462098</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.23696756362915</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>4.011544466018677</v>
+        <v>18.47461676597595</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9983593504958139</v>
+        <v>0.9130844517233803</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9266891891891892</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9193123612301874</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.9787282333085371</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>2.477370738983154</v>
+        <v>34.06773924827576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9983552409841592</v>
+        <v>0.913262433288194</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.9263513513513514</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9934996412139632</v>
+        <v>0.9191034179457824</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.9772424591462098</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Classification</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>4.23696756362915</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9983535762483131</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9935064935064936</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9934996412139632</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>18.47461676597595</v>
+        <v>27.38202667236328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9130844517233803</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9266891891891892</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193123612301874</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9787282333085371</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>34.06773924827576</v>
+        <v>43.14812064170837</v>
       </c>
       <c r="E3" t="n">
-        <v>0.913262433288194</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9263513513513514</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9191034179457824</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9772424591462098</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -619,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>18.47461676597595</v>
+        <v>27.38202667236328</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9130844517233803</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9266891891891892</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9193123612301874</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9787282333085371</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>
@@ -654,26 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>34.06773924827576</v>
+        <v>43.14812064170837</v>
       </c>
       <c r="E3" t="n">
-        <v>0.913262433288194</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9263513513513514</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9191034179457824</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9772424591462098</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 50, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': None, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 12, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
+++ b/output/reports/cv_experiment_RandomForest_kmeans_classification.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>27.38202667236328</v>
+        <v>21.03134727478027</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>43.14812064170837</v>
+        <v>35.0576798915863</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>27.38202667236328</v>
+        <v>21.03134727478027</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>43.14812064170837</v>
+        <v>35.0576798915863</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
